--- a/data/2027 Masters Draft & Scoreboard AZ.xlsx
+++ b/data/2027 Masters Draft & Scoreboard AZ.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft_Import" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft_Helper" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Scoring" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drafted Teams" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Draft_Import" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Draft_Helper" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Team_Scoring" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Team_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Drafted Teams" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Scores" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="6" hidden="1">Scores!$A$1:$K$92</definedName>
